--- a/WHO_Lebanon.xlsx
+++ b/WHO_Lebanon.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E156"/>
+  <dimension ref="A1:E158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -5826,6 +5826,89 @@
         </is>
       </c>
     </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Greece and WHO launch partnership to expand lifesaving hospital care and strengthen critical health services in Lebanon</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>https://www.emro.who.int/lbn/lebanon-news/greece-and-who-launch-partnership-to-expand-lifesaving-hospital-care-and-strengthen-critical-health-services-in-lebanon.html</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Beirut, Lebanon, 13 September 2026 – The Government of the Hellenic Republic, the World Health Organization (WHO) and Saint George University Medical Center launched a new initiative to expand access to lifesaving and limb-saving hospital care for vulnerable patients in Lebanon, while strengthening the hospital’s capacity to deliver high-quality emergency, critical, surgical and neonatal services.
+Supported by a contribution of EUR 500 000 from the Government of the Hellenic Republic, through Hellenic Aid of the Ministry of Foreign Affairs, the 12-month initiative will integrate Saint George University Medical Center into WHO’s national lifesaving and limb-saving hospitalization initiative and provide priority medical equipment to enhance critical hospital services.
+Lebanon’s health system continues to face significant pressures stemming from the country’s prolonged economic crisis, population displacement, health workforce shortages, fragile supply chains and recurrent conflict-related shocks. These pressures have increased financial barriers to accessing specialized and high-cost medical care, particularly for vulnerable and uninsured patients. The new initiative aims to address these barriers while reinforcing the capacity of one of the country’s leading tertiary referral and university medical centres.
+“This partnership demonstrates the importance of ensuring that vulnerable people can access the care they need when they need it, while simultaneously investing in the capacity of health facilities to deliver safe, effective services and high-quality services,” said Dr Ahmed Zouiten, WHO Representative and Head of Mission in Lebanon.
+Through the hospitalization component, WHO will support vulnerable and uninsured patients with life-threatening or limb-threatening conditions requiring emergency, critical, specialized or advanced inpatient care. This may include trauma, cardiac and other critical medical conditions, as well as neonatal cases requiring specialized care, including intensive care and neonatal intensive care, or specialized neonatal transportation between hospitals.
+The initiative will also strengthen the operational capacity of Saint George University Medical Center through the procurement and installation of priority medical equipment.
+These investments will enhance neonatal care during ambulance transport, surgical and anesthesia services, and emergency response capacity, enabling the hospital to manage critically ill patients and complex, high-risk cases more safely and effectively.
+“The Government of the Hellenic Republic, through Hellenic Aid of the Ministry of Foreign Affairs, is pleased to support this initiative as a tangible expression of solidarity with the Lebanese people during a time of need. This support combines immediate assistance for vulnerable patients with a longer-term investment in Lebanon’s health system and the resilience of its hospitals. Greece will continue to stand by the Lebanese people and support Lebanon’s efforts towards recovery, resilience and stability”, said H.E. Despina Koukoulopoulou, Ambassador of Greece to Lebanon.
+Saint George University Medical Center has long served as a major tertiary referral and university medical centre in Lebanon. The facility was also severely affected by the Beirut Port explosion in 2020 and continues its recovery from the devastating impact of that event.
+“As we continue to recover from the series of crises that have affected Lebanon, this generous contribution from our sisters and brothers in the Hellenic Republic, together with our partnership with the World Health Organization will strengthen our ability to care for those who need it the most,” said Dr Ziad Haydar, Chief Executive Officer of Saint George University Medical Center.
+Following the launch, Ms Maya Hobeika, Director of Philanthropic Relations at Saint George University Medical Center, presented the programme’s implementation modalities, highlighting its expected impact on the care of the most vulnerable patients, as well as the measures that will ensure accountability, transparency and effective oversight.
+His Eminence Metropolitan Elias Audi, Archbishop of Beirut and its Dependencies, welcomed the initiative, stating
+“We welcome the launch of this programme, which aims to support lifesaving and limb-saving medical care. Saving a human life, or preserving a limb at risk, is not simply a matter of treating illness. It is about safeguarding the dignity of each person, preserving hope, protecting families, and enabling individuals to continue contributing to their communities. We thank the World Health Organization for its partnership and commitment to health and human well-being, and the Greek Ministry of Foreign Affairs for making this programme possible through its generous support”.
+The project will be implemented by the WHO Country Office, in close coordination with the Saint George University Medical Center, building on WHO’s established hospitalization support mechanisms and existing national health-sector arrangements.
+The partnership reflects the shared commitment to protecting access to essential health services and strengthening the resilience of Lebanon’s health system.</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:21:18.465775+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>From review to reform: Lebanon charts the next phase of health system transformation</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>https://www.emro.who.int/lbn/lebanon-news/from-review-to-reform-lebanon-charts-the-next-phase-of-health-system-transformation.html</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>29 July 2026, Beirut, Lebanon – The Ministry of Public Health, with support from the World Health Organization (WHO) and the European Union (EU), convened a national workshop, From Review to Reform, to assess progress on the implementation of the National Health Strategy – Vision 2030.
+Bringing together government officials, development partners, health experts and decision-makers, the workshop marked the midpoint of the Lebanon’s flagship health strategy, providing an opportunity to review achievements, identify remaining challenges and further finetune the reforms needed to build a stronger, more resilient and equitable health system.
+Opening the workshop, Minister of Public Health Dr Rakan Nassereddine emphasized that Lebanon's health system has continued to advance despite unprecedented economic hardship, disease outbreaks, conflict, displacement and growing humanitarian needs.
+"The progress achieved demonstrates that, when there is political commitment, a clear strategic vision and strong partnerships, reform is possible even in times of crisis. Resilience is not simply about enduring shocks – it is about learning from them and emerging with a stronger health system."
+Dr Nassereddine highlighted advances made over the past year, including progress towards operationalizing the National Medicines Agency, rehabilitation of the Central Public Health Laboratory, advances in emergency preparedness through the Public Health Emergency Operations Centre and in digital health transformation and health technology assessment. He drew attention to the strengthening of public hospitals through infrastructure upgrades, equipment and specialized training, the continued expansion of primary health care services and the achievement of 100% hospital coverage for uninsured patients in public hospitals. The Ministry, he said, remains determined to achieve universal health coverage by 2030.
+EU Head of Cooperation in Lebanon Ms Alessandra Viezzer reaffirmed the EU's longstanding partnership with Lebanon and paid tribute to the resilience demonstrated by the Ministry of Public Health and health workers through successive crises.
+"Health sector reform goes beyond health care itself," she said. "It is also about rebuilding trust between citizens and the state. Strong, accessible public services are fundamental to restoring that trust."
+Ms Viezzer noted that the workshop provided a platform to align priorities for the remaining years of the National Health Strategy, helping to guide future support from development partners. She also hailed the strengthening of the Primary Health Care Network through sustained cooperation between the Ministry, the EU and partners as a major public health success.
+"Health sector reform goes beyond health care itself," she said. "It is also about rebuilding trust between citizens and the state. Strong, accessible public services are fundamental to restoring that trust."
+Ms Viezzer noted that the workshop provided a platform to align priorities for the remaining years of the National Health Strategy, helping to guide future support from development partners. She also hailed the strengthening of the Primary Health Care Network through sustained cooperation between the Ministry, the EU and partners as a major public health success.
+Speaking on behalf of WHO, Acting WHO Representative in Lebanon Dr Yutaro Setoya underlined WHO's long-standing commitment to supporting Lebanon's health system, saying: "For nearly 3 decades, WHO has worked alongside the Government of Lebanon to strengthen every building block of the health system, build national capacities and generate evidence for policy and planning. Our shared objective has always been to build a health system that is responsive to people's needs, adaptable to change and resilient in the face of crises."
+Dr Setoya described the workshop as offering an opportunity to refocus collective efforts around a reform agenda grounded in equity, efficiency, transparency and sustainability.
+Acknowledging the Ministry's progress in strengthening health service delivery, surveillance systems and digital transformation in the face of multiple crises, he emphasized that further work is needed to advance governance, sustainable health financing and the production and retention of the health workforce.
+Looking ahead, Dr Setoya stressed the importance of preparing the health system for emerging challenges, including artificial intelligence, climate change and recurrent emergencies, and that multisectoral coordination, collaboration across government, academia, civil society, the private sector and international partners will be critical to sustaining progress.
+"Universal health coverage is a right, not a luxury," he said. "Governments must strengthen stewardship through appropriate legislation, ensure no one is left behind, maintain facilities and a workforce fit for purpose, and prioritize sustainable and equitable financing."
+Workshop participants engaged in technical sessions reviewing midterm implementation of the National Health Strategy and validating health sector reform agenda priorities. Discussions focused on strengthening governance, financing, service delivery, digital health, workforce development and emergency preparedness, and identifying next steps to accelerate progress toward Vision 2030.</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:21:26.547571+00:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
